--- a/Shemot 5787.xlsx
+++ b/Shemot 5787.xlsx
@@ -2515,11 +2515,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Kaufman</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tisa", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tisa&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -2556,7 +2556,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tisa&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tisa&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -2571,7 +2571,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tisa&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tisa&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -2586,7 +2586,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tisa&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tisa&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -2601,7 +2601,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tisa&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tisa&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -2616,7 +2616,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tisa&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tisa&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -2631,7 +2631,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tisa&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tisa&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -2646,7 +2646,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tisa&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tisa&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -2661,7 +2661,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tisa&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Ki Tisa&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -3031,11 +3031,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Kaufman</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayakhel", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayakhel&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -3072,7 +3072,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayakhel&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayakhel&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -3087,7 +3087,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayakhel&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayakhel&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -3102,7 +3102,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayakhel&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayakhel&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -3117,7 +3117,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayakhel&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayakhel&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -3132,7 +3132,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayakhel&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayakhel&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -3147,7 +3147,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayakhel&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayakhel&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -3162,7 +3162,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayakhel&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayakhel&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -3177,7 +3177,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayakhel&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vayakhel&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -3543,11 +3543,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Kaufman</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pekudei", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pekudei&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -3584,7 +3584,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pekudei&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pekudei&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -3599,7 +3599,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pekudei&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pekudei&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -3614,7 +3614,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pekudei&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pekudei&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -3629,7 +3629,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pekudei&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pekudei&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -3644,7 +3644,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pekudei&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pekudei&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -3659,7 +3659,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pekudei&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pekudei&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -3674,7 +3674,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pekudei&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pekudei&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -3689,7 +3689,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pekudei&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Pekudei&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -4055,11 +4055,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Kaufman</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shemot", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shemot&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -4096,7 +4096,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shemot&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shemot&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -4111,7 +4111,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shemot&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shemot&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -4126,7 +4126,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shemot&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shemot&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -4141,7 +4141,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shemot&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shemot&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -4156,7 +4156,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shemot&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shemot&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -4171,7 +4171,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shemot&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shemot&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -4186,7 +4186,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shemot&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shemot&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -4201,7 +4201,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shemot&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Shemot&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -4571,11 +4571,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Kaufman</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaera", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaera&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -4612,7 +4612,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaera&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaera&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -4627,7 +4627,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaera&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaera&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -4642,7 +4642,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaera&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaera&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -4657,7 +4657,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaera&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaera&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -4672,7 +4672,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaera&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaera&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -4687,7 +4687,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaera&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaera&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -4702,7 +4702,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaera&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaera&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -4717,7 +4717,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaera&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Vaera&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -5083,11 +5083,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Kaufman</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bo", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bo&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -5124,7 +5124,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bo&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bo&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -5139,7 +5139,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bo&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bo&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -5154,7 +5154,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bo&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bo&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -5169,7 +5169,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bo&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bo&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -5184,7 +5184,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bo&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bo&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -5199,7 +5199,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bo&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bo&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -5214,7 +5214,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bo&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bo&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -5229,7 +5229,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bo&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Bo&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -5595,11 +5595,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Kaufman</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Beshalach", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Beshalach&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -5636,7 +5636,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Beshalach&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Beshalach&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -5651,7 +5651,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Beshalach&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Beshalach&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -5666,7 +5666,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Beshalach&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Beshalach&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -5681,7 +5681,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Beshalach&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Beshalach&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -5696,7 +5696,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Beshalach&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Beshalach&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -5711,7 +5711,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Beshalach&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Beshalach&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -5726,7 +5726,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Beshalach&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Beshalach&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -5741,7 +5741,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Beshalach&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Beshalach&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -6107,11 +6107,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Kaufman</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yitro", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yitro&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -6148,7 +6148,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yitro&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yitro&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -6163,7 +6163,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yitro&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yitro&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -6178,7 +6178,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yitro&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yitro&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -6193,7 +6193,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yitro&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yitro&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -6208,7 +6208,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yitro&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yitro&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -6223,7 +6223,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yitro&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yitro&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -6238,7 +6238,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yitro&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yitro&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -6253,7 +6253,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yitro&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Yitro&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -6623,11 +6623,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Kaufman</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Mishpatim", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Mishpatim&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -6664,7 +6664,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Mishpatim&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Mishpatim&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -6679,7 +6679,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Mishpatim&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Mishpatim&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -6694,7 +6694,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Mishpatim&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Mishpatim&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -6709,7 +6709,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Mishpatim&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Mishpatim&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -6724,7 +6724,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Mishpatim&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Mishpatim&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -6739,7 +6739,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Mishpatim&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Mishpatim&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -6754,7 +6754,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Mishpatim&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Mishpatim&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -6769,7 +6769,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Mishpatim&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Mishpatim&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -7135,11 +7135,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Kaufman</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Terumah", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Terumah&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -7176,7 +7176,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Terumah&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Terumah&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -7191,7 +7191,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Terumah&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Terumah&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -7206,7 +7206,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Terumah&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Terumah&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -7221,7 +7221,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Terumah&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Terumah&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -7236,7 +7236,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Terumah&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Terumah&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -7251,7 +7251,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Terumah&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Terumah&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -7266,7 +7266,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Terumah&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Terumah&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -7281,7 +7281,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Terumah&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Terumah&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
@@ -7647,11 +7647,11 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Red</t>
+          <t>Kaufman</t>
         </is>
       </c>
       <c r="C13" s="3">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tetzaveh", "Virtual Tikkun")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;view=both&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tetzaveh&amp;join=24A677PXECFW", "Virtual Tikkun")</f>
         <v/>
       </c>
       <c r="D13" s="3" t="inlineStr"/>
@@ -7688,7 +7688,7 @@
     </row>
     <row r="15">
       <c r="A15" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tetzaveh&amp;aliyah=A1", "I")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tetzaveh&amp;aliyah=A1&amp;join=24A677PXECFW", "I")</f>
         <v/>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -7703,7 +7703,7 @@
     </row>
     <row r="16">
       <c r="A16" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tetzaveh&amp;aliyah=A2", "II")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tetzaveh&amp;aliyah=A2&amp;join=24A677PXECFW", "II")</f>
         <v/>
       </c>
       <c r="B16" s="12" t="inlineStr">
@@ -7718,7 +7718,7 @@
     </row>
     <row r="17">
       <c r="A17" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tetzaveh&amp;aliyah=A3", "III")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tetzaveh&amp;aliyah=A3&amp;join=24A677PXECFW", "III")</f>
         <v/>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -7733,7 +7733,7 @@
     </row>
     <row r="18">
       <c r="A18" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tetzaveh&amp;aliyah=A4", "IV")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tetzaveh&amp;aliyah=A4&amp;join=24A677PXECFW", "IV")</f>
         <v/>
       </c>
       <c r="B18" s="10" t="inlineStr">
@@ -7748,7 +7748,7 @@
     </row>
     <row r="19">
       <c r="A19" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tetzaveh&amp;aliyah=A5", "V")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tetzaveh&amp;aliyah=A5&amp;join=24A677PXECFW", "V")</f>
         <v/>
       </c>
       <c r="B19" s="12" t="inlineStr">
@@ -7763,7 +7763,7 @@
     </row>
     <row r="20">
       <c r="A20" s="13">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tetzaveh&amp;aliyah=A6", "VI")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tetzaveh&amp;aliyah=A6&amp;join=24A677PXECFW", "VI")</f>
         <v/>
       </c>
       <c r="B20" s="14" t="inlineStr">
@@ -7778,7 +7778,7 @@
     </row>
     <row r="21">
       <c r="A21" s="9">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tetzaveh&amp;aliyah=A7", "VII")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tetzaveh&amp;aliyah=A7&amp;join=24A677PXECFW", "VII")</f>
         <v/>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -7793,7 +7793,7 @@
     </row>
     <row r="22">
       <c r="A22" s="11">
-        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tetzaveh&amp;aliyah=M", "Maf")</f>
+        <f>hyperlink("https://myvirtualtikkun.com/?shul=cbssf&amp;scroll="&amp;$B$13&amp;"&amp;parsha=Tetzaveh&amp;aliyah=M&amp;join=24A677PXECFW", "Maf")</f>
         <v/>
       </c>
       <c r="B22" s="12" t="inlineStr">
